--- a/assets/files/templates/SafePlum_near_miss.xlsx
+++ b/assets/files/templates/SafePlum_near_miss.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="73">
   <si>
     <r>
       <rPr>
@@ -524,9 +524,6 @@
     <t xml:space="preserve">발생 일시</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-27 10:20</t>
-  </si>
-  <si>
     <t xml:space="preserve">발생 장소</t>
   </si>
   <si>
@@ -1309,9 +1306,6 @@
     <t xml:space="preserve">상태</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-27</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <i val="true"/>
@@ -1403,9 +1397,6 @@
   </si>
   <si>
     <t xml:space="preserve">물류팀</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-11-03</t>
   </si>
   <si>
     <t xml:space="preserve">수시평가 반영</t>
@@ -2407,61 +2398,61 @@
       <c r="A4" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="11" t="s">
-        <v>16</v>
+      <c r="B4" s="11" t="n">
+        <v>46322.4305555556</v>
       </c>
       <c r="C4" s="11"/>
       <c r="D4" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="12" t="s">
         <v>17</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>18</v>
       </c>
       <c r="F4" s="12"/>
     </row>
     <row r="5" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B5" s="13"/>
       <c r="C5" s="13"/>
       <c r="D5" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E5" s="14"/>
       <c r="F5" s="14"/>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
       <c r="D6" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E6" s="13"/>
       <c r="F6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="12" t="s">
         <v>23</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>24</v>
       </c>
       <c r="C7" s="12"/>
       <c r="D7" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="12" t="s">
         <v>25</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>26</v>
       </c>
       <c r="F7" s="12"/>
     </row>
     <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B9" s="15"/>
       <c r="C9" s="15"/>
@@ -2471,7 +2462,7 @@
     </row>
     <row r="10" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B10" s="16"/>
       <c r="C10" s="16"/>
@@ -2481,7 +2472,7 @@
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B12" s="15"/>
       <c r="C12" s="15"/>
@@ -2491,10 +2482,10 @@
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="12" t="s">
         <v>30</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>31</v>
       </c>
       <c r="C13" s="12"/>
       <c r="D13" s="12"/>
@@ -2503,10 +2494,10 @@
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" s="12" t="s">
         <v>32</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>33</v>
       </c>
       <c r="C14" s="12"/>
       <c r="D14" s="12"/>
@@ -2515,10 +2506,10 @@
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="12" t="s">
         <v>34</v>
-      </c>
-      <c r="B15" s="12" t="s">
-        <v>35</v>
       </c>
       <c r="C15" s="12"/>
       <c r="D15" s="12"/>
@@ -2527,7 +2518,7 @@
     </row>
     <row r="17" customFormat="false" ht="16.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B17" s="15"/>
       <c r="C17" s="15"/>
@@ -2537,7 +2528,7 @@
     </row>
     <row r="18" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B18" s="16"/>
       <c r="C18" s="16"/>
@@ -2547,7 +2538,7 @@
     </row>
     <row r="20" customFormat="false" ht="16.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B20" s="15"/>
       <c r="C20" s="15"/>
@@ -2565,31 +2556,31 @@
     </row>
     <row r="23" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
       <c r="D23" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E23" s="13"/>
       <c r="F23" s="13"/>
     </row>
     <row r="24" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B24" s="13"/>
       <c r="C24" s="13"/>
       <c r="D24" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E24" s="13"/>
       <c r="F24" s="13"/>
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="19" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B26" s="19"/>
       <c r="C26" s="19"/>
@@ -2677,7 +2668,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2691,15 +2682,15 @@
         <v>11</v>
       </c>
       <c r="L1" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="M1" s="7" t="s">
         <v>45</v>
-      </c>
-      <c r="M1" s="7" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -2715,7 +2706,7 @@
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="19" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -2732,79 +2723,79 @@
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="C5" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="D5" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="D5" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="10" t="s">
+      <c r="F5" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F5" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5" s="10" t="s">
+      <c r="H5" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="H5" s="10" t="s">
+      <c r="I5" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="K5" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="I5" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="J5" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="K5" s="10" t="s">
+      <c r="L5" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="L5" s="10" t="s">
+      <c r="M5" s="10" t="s">
         <v>55</v>
-      </c>
-      <c r="M5" s="10" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="22" t="n">
+        <v>46322</v>
+      </c>
+      <c r="C6" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="F6" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="C6" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="12" t="s">
+      <c r="H6" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="F6" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="G6" s="12" t="s">
+      <c r="I6" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="H6" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="I6" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="J6" s="22" t="s">
-        <v>62</v>
+      <c r="J6" s="22" t="n">
+        <v>46329</v>
       </c>
       <c r="K6" s="24"/>
       <c r="L6" s="23" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="M6" s="25" t="str">
         <f aca="true">IF(E6="","",IF(K6&lt;&gt;"","완료",IF(J6="","기한 미정",IF(J6&lt;TODAY(),"기한 경과","진행 중"))))</f>
@@ -3473,47 +3464,47 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="27" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="28" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C42" s="29" t="n">
         <f aca="false">COUNTIF($D$6:$D$39,"떨어짐")</f>
         <v>0</v>
       </c>
       <c r="D42" s="28" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E42" s="29" t="n">
         <f aca="false">COUNTIF($D$6:$D$39,"넘어짐")</f>
         <v>0</v>
       </c>
       <c r="F42" s="28" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G42" s="29" t="n">
         <f aca="false">COUNTIF($D$6:$D$39,"끼임")</f>
         <v>0</v>
       </c>
       <c r="H42" s="28" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I42" s="29" t="n">
         <f aca="false">COUNTIF($D$6:$D$39,"부딪힘")</f>
         <v>0</v>
       </c>
       <c r="J42" s="28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K42" s="29" t="n">
         <f aca="false">COUNTIF($D$6:$D$39,"물체에 맞음")</f>
         <v>1</v>
       </c>
       <c r="L42" s="28" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="M42" s="29" t="n">
         <f aca="false">COUNTIF($D$6:$D$39,"무너짐")</f>
@@ -3522,42 +3513,42 @@
     </row>
     <row r="43" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="28" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C43" s="29" t="n">
         <f aca="false">COUNTIF($D$6:$D$39,"깔림·뒤집힘")</f>
         <v>0</v>
       </c>
       <c r="D43" s="28" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E43" s="29" t="n">
         <f aca="false">COUNTIF($D$6:$D$39,"절단·베임·찔림")</f>
         <v>0</v>
       </c>
       <c r="F43" s="28" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G43" s="29" t="n">
         <f aca="false">COUNTIF($D$6:$D$39,"감전")</f>
         <v>0</v>
       </c>
       <c r="H43" s="28" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="I43" s="29" t="n">
         <f aca="false">COUNTIF($D$6:$D$39,"화재·폭발")</f>
         <v>0</v>
       </c>
       <c r="J43" s="28" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="K43" s="29" t="n">
         <f aca="false">COUNTIF($D$6:$D$39,"화학물질 누출·접촉")</f>
         <v>0</v>
       </c>
       <c r="L43" s="28" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="M43" s="29" t="n">
         <f aca="false">COUNTIF($D$6:$D$39,"기타")</f>

--- a/assets/files/templates/SafePlum_near_miss.xlsx
+++ b/assets/files/templates/SafePlum_near_miss.xlsx
@@ -2305,12 +2305,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="5" t="s">
         <v>5</v>
       </c>
@@ -2323,12 +2323,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="5" t="s">
         <v>8</v>
       </c>
